--- a/config/bms/BAU_协能.xlsx
+++ b/config/bms/BAU_协能.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="129">
   <si>
     <t>序号</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>BMS系统故障汇总</t>
+  </si>
+  <si>
+    <t>U16</t>
   </si>
   <si>
     <t>InputRegisters</t>
@@ -503,21 +506,42 @@
     <t>系统总电压</t>
   </si>
   <si>
+    <t>I16</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
     <t>系统总电流</t>
   </si>
   <si>
+    <t>I32</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>系统SOC</t>
   </si>
   <si>
+    <t>‰</t>
+  </si>
+  <si>
     <t>系统SOH</t>
   </si>
   <si>
     <t>系统绝缘值</t>
   </si>
   <si>
+    <t>KΩ</t>
+  </si>
+  <si>
     <t>系统可充电量</t>
   </si>
   <si>
+    <t>kwh</t>
+  </si>
+  <si>
     <t>系统可放电量</t>
   </si>
   <si>
@@ -533,6 +557,9 @@
     <t>簇间总压差异值</t>
   </si>
   <si>
+    <t>v</t>
+  </si>
+  <si>
     <t>系统最高电压电池所在Rack号</t>
   </si>
   <si>
@@ -545,6 +572,9 @@
     <t>系统最高电池电压</t>
   </si>
   <si>
+    <t>mv</t>
+  </si>
+  <si>
     <t>系统最低电压电池所在Rack号</t>
   </si>
   <si>
@@ -572,6 +602,9 @@
     <t>系统最高电池温度</t>
   </si>
   <si>
+    <t>℃</t>
+  </si>
+  <si>
     <t>系统最低温度电池所在Rack号</t>
   </si>
   <si>
@@ -587,16 +620,16 @@
     <t>系统平均温度</t>
   </si>
   <si>
-    <t>累计充电电量高位</t>
-  </si>
-  <si>
-    <t>累计充电电量低位</t>
-  </si>
-  <si>
-    <t>累计放电电量高位</t>
-  </si>
-  <si>
-    <t>累计放电电量低位</t>
+    <t>累计充电电量</t>
+  </si>
+  <si>
+    <t>U32</t>
+  </si>
+  <si>
+    <t>kWh</t>
+  </si>
+  <si>
+    <t>累计放电电量</t>
   </si>
   <si>
     <t>当前在网簇数</t>
@@ -611,6 +644,9 @@
     <t>堆可用放电功率</t>
   </si>
   <si>
+    <t>kw</t>
+  </si>
+  <si>
     <t>堆可用充电功率</t>
   </si>
   <si>
@@ -627,9 +663,6 @@
   </si>
   <si>
     <t>电池组数</t>
-  </si>
-  <si>
-    <t>U16</t>
   </si>
   <si>
     <t/>
@@ -654,7 +687,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -680,13 +713,18 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -847,7 +885,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -863,6 +901,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1053,7 +1097,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1083,6 +1127,19 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1098,6 +1155,21 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1218,55 +1290,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1281,74 +1350,77 @@
     <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1394,34 +1466,52 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1949,11 +2039,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P240"/>
+  <dimension ref="A1:P238"/>
   <sheetFormatPr defaultColWidth="9.03100775193798" defaultRowHeight="18.4"/>
   <cols>
     <col min="1" max="1" width="9.03100775193798" style="3"/>
-    <col min="2" max="2" width="28.3565891472868" style="15" customWidth="1"/>
+    <col min="2" max="2" width="28.3565891472868" style="16" customWidth="1"/>
     <col min="3" max="5" width="9.03100775193798" style="3"/>
     <col min="6" max="6" width="10.1007751937984" style="3" customWidth="1"/>
     <col min="7" max="7" width="14.3875968992248" style="3" customWidth="1"/>
@@ -2021,330 +2111,426 @@
       <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="12"/>
+      <c r="C2" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
       <c r="F2" s="12">
         <v>4097</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H2" s="12">
+        <v>1</v>
+      </c>
       <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
+      <c r="J2" s="12">
+        <v>1</v>
+      </c>
+      <c r="K2" s="12">
+        <v>0</v>
+      </c>
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
-      <c r="P2" s="17" t="s">
-        <v>18</v>
+      <c r="P2" s="18" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" s="8" customFormat="1" ht="294.45" spans="1:16">
       <c r="A3" s="12">
         <v>2</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="12"/>
+      <c r="B3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
       <c r="F3" s="12">
         <v>4098</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H3" s="12">
+        <v>1</v>
+      </c>
       <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
+      <c r="J3" s="12">
+        <v>1</v>
+      </c>
+      <c r="K3" s="12">
+        <v>0</v>
+      </c>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="12"/>
-      <c r="P3" s="17" t="s">
-        <v>20</v>
+      <c r="P3" s="18" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" s="8" customFormat="1" ht="294.45" spans="1:16">
       <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="12"/>
+      <c r="B4" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="12">
         <v>4099</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H4" s="12">
+        <v>1</v>
+      </c>
       <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
+      <c r="J4" s="12">
+        <v>1</v>
+      </c>
+      <c r="K4" s="12">
+        <v>0</v>
+      </c>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="12"/>
-      <c r="P4" s="17" t="s">
-        <v>22</v>
+      <c r="P4" s="18" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" s="8" customFormat="1" ht="295.2" spans="1:16">
       <c r="A5" s="12">
         <v>4</v>
       </c>
-      <c r="B5" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="12"/>
+      <c r="B5" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
       <c r="F5" s="12">
         <v>4100</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H5" s="12">
+        <v>1</v>
+      </c>
       <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="J5" s="12">
+        <v>1</v>
+      </c>
+      <c r="K5" s="12">
+        <v>0</v>
+      </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="12"/>
-      <c r="P5" s="17" t="s">
-        <v>24</v>
+      <c r="P5" s="18" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6" s="8" customFormat="1" ht="295.2" spans="1:16">
       <c r="A6" s="12">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="12"/>
+      <c r="B6" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12">
         <v>4101</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H6" s="12">
+        <v>1</v>
+      </c>
       <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
+      <c r="J6" s="12">
+        <v>1</v>
+      </c>
+      <c r="K6" s="12">
+        <v>0</v>
+      </c>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="12"/>
-      <c r="P6" s="17" t="s">
-        <v>26</v>
+      <c r="P6" s="18" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" s="8" customFormat="1" ht="295.2" spans="1:16">
       <c r="A7" s="12">
         <v>6</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="12"/>
+      <c r="B7" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
       <c r="F7" s="12">
         <v>4102</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H7" s="12">
+        <v>1</v>
+      </c>
       <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
+      <c r="J7" s="12">
+        <v>1</v>
+      </c>
+      <c r="K7" s="12">
+        <v>0</v>
+      </c>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="12"/>
-      <c r="P7" s="17" t="s">
-        <v>28</v>
+      <c r="P7" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8" s="8" customFormat="1" ht="294.45" spans="1:16">
       <c r="A8" s="12">
         <v>7</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="12"/>
+      <c r="B8" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12">
         <v>4103</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H8" s="12">
+        <v>1</v>
+      </c>
       <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
+      <c r="J8" s="12">
+        <v>1</v>
+      </c>
+      <c r="K8" s="12">
+        <v>0</v>
+      </c>
       <c r="L8" s="12"/>
       <c r="M8" s="12"/>
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
-      <c r="P8" s="17" t="s">
-        <v>30</v>
+      <c r="P8" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" s="8" customFormat="1" ht="294.45" spans="1:16">
       <c r="A9" s="12">
         <v>8</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="12"/>
+      <c r="B9" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D9" s="12"/>
       <c r="E9" s="12"/>
       <c r="F9" s="12">
         <v>4104</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H9" s="12">
+        <v>1</v>
+      </c>
       <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
+      <c r="J9" s="12">
+        <v>1</v>
+      </c>
+      <c r="K9" s="12">
+        <v>0</v>
+      </c>
       <c r="L9" s="12"/>
       <c r="M9" s="12"/>
       <c r="N9" s="12"/>
       <c r="O9" s="12"/>
-      <c r="P9" s="17" t="s">
-        <v>32</v>
+      <c r="P9" s="18" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="10" s="8" customFormat="1" ht="294.45" spans="1:16">
       <c r="A10" s="12">
         <v>9</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="12"/>
+      <c r="B10" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>
       <c r="F10" s="12">
         <v>4105</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H10" s="12">
+        <v>1</v>
+      </c>
       <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
+      <c r="J10" s="12">
+        <v>1</v>
+      </c>
+      <c r="K10" s="12">
+        <v>0</v>
+      </c>
       <c r="L10" s="12"/>
       <c r="M10" s="12"/>
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
-      <c r="P10" s="17" t="s">
-        <v>34</v>
+      <c r="P10" s="18" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="11" s="8" customFormat="1" ht="294.45" spans="1:16">
       <c r="A11" s="12">
         <v>10</v>
       </c>
-      <c r="B11" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="12"/>
+      <c r="B11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D11" s="12"/>
       <c r="E11" s="12"/>
       <c r="F11" s="12">
         <v>4108</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H11" s="12">
+        <v>1</v>
+      </c>
       <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
+      <c r="J11" s="12">
+        <v>1</v>
+      </c>
+      <c r="K11" s="12">
+        <v>0</v>
+      </c>
       <c r="L11" s="12"/>
       <c r="M11" s="12"/>
       <c r="N11" s="12"/>
       <c r="O11" s="12"/>
-      <c r="P11" s="17" t="s">
-        <v>36</v>
+      <c r="P11" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="12" s="8" customFormat="1" ht="294.45" spans="1:16">
       <c r="A12" s="12">
         <v>11</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="12"/>
+      <c r="B12" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
       <c r="F12" s="12">
         <v>4108</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H12" s="12">
+        <v>1</v>
+      </c>
       <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
+      <c r="J12" s="12">
+        <v>1</v>
+      </c>
+      <c r="K12" s="12">
+        <v>0</v>
+      </c>
       <c r="L12" s="12"/>
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
-      <c r="P12" s="17" t="s">
-        <v>38</v>
+      <c r="P12" s="18" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="13" s="8" customFormat="1" spans="1:16">
       <c r="A13" s="12">
         <v>12</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="12"/>
+      <c r="B13" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
       <c r="F13" s="12">
         <v>4112</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H13" s="12">
+        <v>1</v>
+      </c>
       <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
+      <c r="J13" s="12">
+        <v>1</v>
+      </c>
+      <c r="K13" s="12">
+        <v>0</v>
+      </c>
       <c r="L13" s="12"/>
       <c r="M13" s="12"/>
       <c r="N13" s="12"/>
@@ -2355,22 +2541,30 @@
       <c r="A14" s="12">
         <v>13</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="12"/>
+      <c r="B14" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
       <c r="F14" s="12">
         <v>4113</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H14" s="12">
+        <v>1</v>
+      </c>
       <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
+      <c r="J14" s="12">
+        <v>1</v>
+      </c>
+      <c r="K14" s="12">
+        <v>0</v>
+      </c>
       <c r="L14" s="12"/>
       <c r="M14" s="12"/>
       <c r="N14" s="12"/>
@@ -2381,22 +2575,30 @@
       <c r="A15" s="12">
         <v>14</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="12"/>
+      <c r="B15" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12">
         <v>4114</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H15" s="12">
+        <v>1</v>
+      </c>
       <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
+      <c r="J15" s="12">
+        <v>1</v>
+      </c>
+      <c r="K15" s="12">
+        <v>0</v>
+      </c>
       <c r="L15" s="12"/>
       <c r="M15" s="12"/>
       <c r="N15" s="12"/>
@@ -2407,22 +2609,30 @@
       <c r="A16" s="12">
         <v>15</v>
       </c>
-      <c r="B16" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="12"/>
+      <c r="B16" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
       <c r="F16" s="12">
         <v>4115</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H16" s="12">
+        <v>1</v>
+      </c>
       <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
+      <c r="J16" s="12">
+        <v>1</v>
+      </c>
+      <c r="K16" s="12">
+        <v>0</v>
+      </c>
       <c r="L16" s="12"/>
       <c r="M16" s="12"/>
       <c r="N16" s="12"/>
@@ -2433,22 +2643,30 @@
       <c r="A17" s="12">
         <v>16</v>
       </c>
-      <c r="B17" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="12"/>
+      <c r="B17" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12">
         <v>4116</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H17" s="12">
+        <v>1</v>
+      </c>
       <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
+      <c r="J17" s="12">
+        <v>1</v>
+      </c>
+      <c r="K17" s="12">
+        <v>0</v>
+      </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
@@ -2459,22 +2677,30 @@
       <c r="A18" s="12">
         <v>17</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="12"/>
+      <c r="B18" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
       <c r="F18" s="12">
         <v>4136</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H18" s="12">
+        <v>1</v>
+      </c>
       <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
+      <c r="J18" s="12">
+        <v>1</v>
+      </c>
+      <c r="K18" s="12">
+        <v>0</v>
+      </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12"/>
       <c r="N18" s="12"/>
@@ -2485,22 +2711,30 @@
       <c r="A19" s="12">
         <v>18</v>
       </c>
-      <c r="B19" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="12"/>
+      <c r="B19" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D19" s="12"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12">
         <v>4137</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H19" s="12">
+        <v>1</v>
+      </c>
       <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
+      <c r="J19" s="12">
+        <v>1</v>
+      </c>
+      <c r="K19" s="12">
+        <v>0</v>
+      </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
@@ -2511,22 +2745,30 @@
       <c r="A20" s="12">
         <v>19</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="12"/>
+      <c r="B20" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D20" s="12"/>
       <c r="E20" s="12"/>
       <c r="F20" s="12">
         <v>4138</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H20" s="12">
+        <v>1</v>
+      </c>
       <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
+      <c r="J20" s="12">
+        <v>1</v>
+      </c>
+      <c r="K20" s="12">
+        <v>0</v>
+      </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12"/>
       <c r="N20" s="12"/>
@@ -2537,22 +2779,30 @@
       <c r="A21" s="12">
         <v>20</v>
       </c>
-      <c r="B21" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="12"/>
+      <c r="B21" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D21" s="12"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12">
         <v>4141</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H21" s="12">
+        <v>1</v>
+      </c>
       <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
+      <c r="J21" s="12">
+        <v>1</v>
+      </c>
+      <c r="K21" s="12">
+        <v>0</v>
+      </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
@@ -2563,22 +2813,30 @@
       <c r="A22" s="12">
         <v>21</v>
       </c>
-      <c r="B22" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="12"/>
+      <c r="B22" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12">
         <v>4142</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H22" s="12">
+        <v>1</v>
+      </c>
       <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
+      <c r="J22" s="12">
+        <v>1</v>
+      </c>
+      <c r="K22" s="12">
+        <v>0</v>
+      </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
       <c r="N22" s="12"/>
@@ -2589,22 +2847,30 @@
       <c r="A23" s="12">
         <v>22</v>
       </c>
-      <c r="B23" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="12"/>
+      <c r="B23" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12">
         <v>4145</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H23" s="12">
+        <v>1</v>
+      </c>
       <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
+      <c r="J23" s="12">
+        <v>1</v>
+      </c>
+      <c r="K23" s="12">
+        <v>0</v>
+      </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12"/>
       <c r="N23" s="12"/>
@@ -2615,22 +2881,30 @@
       <c r="A24" s="12">
         <v>23</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" s="12"/>
+      <c r="B24" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
       <c r="F24" s="12">
         <v>4146</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H24" s="12">
+        <v>1</v>
+      </c>
       <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
+      <c r="J24" s="12">
+        <v>1</v>
+      </c>
+      <c r="K24" s="12">
+        <v>0</v>
+      </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12"/>
       <c r="N24" s="12"/>
@@ -2641,22 +2915,30 @@
       <c r="A25" s="12">
         <v>24</v>
       </c>
-      <c r="B25" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="12"/>
+      <c r="B25" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D25" s="12"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12">
         <v>4147</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H25" s="12">
+        <v>1</v>
+      </c>
       <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
+      <c r="J25" s="12">
+        <v>1</v>
+      </c>
+      <c r="K25" s="12">
+        <v>0</v>
+      </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12"/>
       <c r="N25" s="12"/>
@@ -2667,22 +2949,30 @@
       <c r="A26" s="12">
         <v>25</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="12"/>
+      <c r="B26" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D26" s="12"/>
       <c r="E26" s="12"/>
       <c r="F26" s="12">
         <v>4148</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H26" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H26" s="12">
+        <v>1</v>
+      </c>
       <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
+      <c r="J26" s="12">
+        <v>1</v>
+      </c>
+      <c r="K26" s="12">
+        <v>0</v>
+      </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12"/>
       <c r="N26" s="12"/>
@@ -2693,22 +2983,30 @@
       <c r="A27" s="12">
         <v>26</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="12"/>
+      <c r="B27" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12">
         <v>4149</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H27" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H27" s="12">
+        <v>1</v>
+      </c>
       <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
+      <c r="J27" s="12">
+        <v>1</v>
+      </c>
+      <c r="K27" s="12">
+        <v>0</v>
+      </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12"/>
       <c r="N27" s="12"/>
@@ -2719,26 +3017,32 @@
       <c r="A28" s="12">
         <v>27</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="12"/>
+      <c r="B28" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D28" s="12"/>
-      <c r="E28" s="21" t="s">
-        <v>55</v>
+      <c r="E28" s="22" t="s">
+        <v>56</v>
       </c>
       <c r="F28" s="12">
         <v>4150</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H28" s="12">
         <v>64</v>
       </c>
       <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
+      <c r="J28" s="12">
+        <v>1</v>
+      </c>
+      <c r="K28" s="12">
+        <v>0</v>
+      </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12"/>
       <c r="N28" s="12"/>
@@ -2749,26 +3053,32 @@
       <c r="A29" s="12">
         <v>28</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="12"/>
+      <c r="B29" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D29" s="12"/>
-      <c r="E29" s="21" t="s">
-        <v>57</v>
+      <c r="E29" s="22" t="s">
+        <v>58</v>
       </c>
       <c r="F29" s="12">
         <v>4214</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H29" s="12">
         <v>64</v>
       </c>
       <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
+      <c r="J29" s="12">
+        <v>1</v>
+      </c>
+      <c r="K29" s="12">
+        <v>0</v>
+      </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
@@ -2779,563 +3089,1312 @@
       <c r="A30" s="12">
         <v>29</v>
       </c>
-      <c r="B30" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="12"/>
+      <c r="B30" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D30" s="12"/>
       <c r="E30" s="12"/>
       <c r="F30" s="12">
         <v>4281</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H30" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H30" s="12">
+        <v>1</v>
+      </c>
       <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
+      <c r="J30" s="12">
+        <v>1</v>
+      </c>
+      <c r="K30" s="12">
+        <v>0</v>
+      </c>
       <c r="L30" s="12"/>
       <c r="M30" s="12"/>
       <c r="N30" s="12"/>
       <c r="O30" s="12"/>
-      <c r="P30" s="17" t="s">
-        <v>59</v>
+      <c r="P30" s="18" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="31" s="8" customFormat="1" ht="294.45" spans="1:16">
       <c r="A31" s="12">
         <v>30</v>
       </c>
-      <c r="B31" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="12"/>
+      <c r="B31" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D31" s="12"/>
       <c r="E31" s="12"/>
       <c r="F31" s="12">
         <v>4282</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H31" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H31" s="12">
+        <v>1</v>
+      </c>
       <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
+      <c r="J31" s="12">
+        <v>1</v>
+      </c>
+      <c r="K31" s="12">
+        <v>0</v>
+      </c>
       <c r="L31" s="12"/>
       <c r="M31" s="12"/>
       <c r="N31" s="12"/>
       <c r="O31" s="12"/>
-      <c r="P31" s="17" t="s">
-        <v>61</v>
+      <c r="P31" s="18" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="32" s="8" customFormat="1" ht="294.45" spans="1:16">
       <c r="A32" s="12">
         <v>31</v>
       </c>
-      <c r="B32" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="12"/>
+      <c r="B32" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D32" s="12"/>
       <c r="E32" s="12"/>
       <c r="F32" s="12">
         <v>4283</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H32" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H32" s="12">
+        <v>1</v>
+      </c>
       <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
+      <c r="J32" s="12">
+        <v>1</v>
+      </c>
+      <c r="K32" s="12">
+        <v>0</v>
+      </c>
       <c r="L32" s="12"/>
       <c r="M32" s="12"/>
       <c r="N32" s="12"/>
       <c r="O32" s="12"/>
-      <c r="P32" s="17" t="s">
-        <v>63</v>
+      <c r="P32" s="18" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="33" s="8" customFormat="1" ht="276" spans="1:16">
       <c r="A33" s="12">
         <v>32</v>
       </c>
-      <c r="B33" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="12"/>
+      <c r="B33" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D33" s="12"/>
       <c r="E33" s="12"/>
       <c r="F33" s="12">
         <v>4284</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H33" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H33" s="12">
+        <v>1</v>
+      </c>
       <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
+      <c r="J33" s="12">
+        <v>1</v>
+      </c>
+      <c r="K33" s="12">
+        <v>0</v>
+      </c>
       <c r="L33" s="12"/>
       <c r="M33" s="12"/>
       <c r="N33" s="12"/>
       <c r="O33" s="12"/>
-      <c r="P33" s="17" t="s">
-        <v>65</v>
+      <c r="P33" s="18" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="34" s="8" customFormat="1" ht="276" spans="1:16">
       <c r="A34" s="12">
         <v>33</v>
       </c>
-      <c r="B34" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" s="12"/>
+      <c r="B34" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D34" s="12"/>
       <c r="E34" s="12"/>
       <c r="F34" s="12">
         <v>4285</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H34" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H34" s="12">
+        <v>1</v>
+      </c>
       <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
+      <c r="J34" s="12">
+        <v>1</v>
+      </c>
+      <c r="K34" s="12">
+        <v>0</v>
+      </c>
       <c r="L34" s="12"/>
       <c r="M34" s="12"/>
       <c r="N34" s="12"/>
       <c r="O34" s="12"/>
-      <c r="P34" s="17" t="s">
-        <v>67</v>
+      <c r="P34" s="18" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="35" s="8" customFormat="1" ht="276" spans="1:16">
       <c r="A35" s="12">
         <v>34</v>
       </c>
-      <c r="B35" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" s="12"/>
+      <c r="B35" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>17</v>
+      </c>
       <c r="D35" s="12"/>
       <c r="E35" s="12"/>
       <c r="F35" s="12">
         <v>4286</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="H35" s="12">
+        <v>1</v>
+      </c>
       <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
+      <c r="J35" s="12">
+        <v>1</v>
+      </c>
+      <c r="K35" s="12">
+        <v>0</v>
+      </c>
       <c r="L35" s="12"/>
       <c r="M35" s="12"/>
       <c r="N35" s="12"/>
       <c r="O35" s="12"/>
-      <c r="P35" s="17" t="s">
-        <v>69</v>
+      <c r="P35" s="18" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:16">
-      <c r="B36" t="s">
-        <v>70</v>
+      <c r="B36" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F36" s="3">
+        <v>8193</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="12">
+        <v>1</v>
+      </c>
+      <c r="J36" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K36" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:16">
-      <c r="B37" t="s">
-        <v>71</v>
+      <c r="B37" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="3">
+        <v>8194</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="3">
+        <v>2</v>
+      </c>
+      <c r="J37" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K37" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:16">
-      <c r="B38" t="s">
+      <c r="B38" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F38" s="3">
+        <v>8196</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="3">
+        <v>1</v>
+      </c>
+      <c r="J38" s="3">
+        <v>1</v>
+      </c>
+      <c r="K38" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="B39" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F39" s="3">
+        <v>8197</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" s="3">
+        <v>2</v>
+      </c>
+      <c r="J39" s="3">
+        <v>1</v>
+      </c>
+      <c r="K39" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="B40" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40" s="3">
+        <v>8198</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="3">
+        <v>1</v>
+      </c>
+      <c r="J40" s="3">
+        <v>1</v>
+      </c>
+      <c r="K40" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="B41" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F41" s="3">
+        <v>8199</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1</v>
+      </c>
+      <c r="J41" s="3">
+        <v>1</v>
+      </c>
+      <c r="K41" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="B42" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" s="3">
+        <v>8200</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="3">
+        <v>1</v>
+      </c>
+      <c r="J42" s="3">
+        <v>1</v>
+      </c>
+      <c r="K42" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="B43" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F43" s="3">
+        <v>8201</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1</v>
+      </c>
+      <c r="J43" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K43" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="B44" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F44" s="3">
+        <v>8202</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="3">
+        <v>1</v>
+      </c>
+      <c r="J44" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K44" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="B45" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="F45" s="3">
+        <v>8203</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K45" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="B46" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="F46" s="3">
+        <v>8204</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="3">
+        <v>1</v>
+      </c>
+      <c r="J46" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K46" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="B47" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C47" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="3">
+        <v>8205</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="3">
+        <v>1</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1</v>
+      </c>
+      <c r="K47" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="B48" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="3">
+        <v>8206</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="3">
+        <v>1</v>
+      </c>
+      <c r="J48" s="3">
+        <v>1</v>
+      </c>
+      <c r="K48" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11">
+      <c r="B49" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" s="3">
+        <v>8207</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1</v>
+      </c>
+      <c r="J49" s="3">
+        <v>1</v>
+      </c>
+      <c r="K49" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11">
+      <c r="B50" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="39" spans="1:16">
-      <c r="B39" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16">
-      <c r="B40" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16">
-      <c r="B41" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16">
-      <c r="B42" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16">
-      <c r="B43" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16">
-      <c r="B44" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16">
-      <c r="B45" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16">
-      <c r="B46" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16">
-      <c r="B47" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
-      <c r="B48" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2">
-      <c r="B49" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2">
-      <c r="B50" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2">
-      <c r="B51" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2">
-      <c r="B52" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2">
-      <c r="B54" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2">
-      <c r="B55" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2">
-      <c r="B56" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2">
-      <c r="B57" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2">
-      <c r="B58" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2">
-      <c r="B59" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2">
-      <c r="B60" t="s">
+      <c r="D50" s="3" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="61" spans="2:2">
-      <c r="B61" t="s">
+      <c r="F50" s="3">
+        <v>8208</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50" s="3">
+        <v>1</v>
+      </c>
+      <c r="J50" s="3">
+        <v>1</v>
+      </c>
+      <c r="K50" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11">
+      <c r="B51" s="23" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="62" spans="2:2">
-      <c r="B62" t="s">
+      <c r="C51" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" s="3">
+        <v>8209</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" s="3">
+        <v>1</v>
+      </c>
+      <c r="J51" s="3">
+        <v>1</v>
+      </c>
+      <c r="K51" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11">
+      <c r="B52" s="23" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="63" spans="2:2">
-      <c r="B63" t="s">
+      <c r="C52" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" s="3">
+        <v>8210</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="3">
+        <v>1</v>
+      </c>
+      <c r="J52" s="3">
+        <v>1</v>
+      </c>
+      <c r="K52" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11">
+      <c r="B53" s="23" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="64" spans="2:2">
-      <c r="B64" t="s">
+      <c r="C53" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="3">
+        <v>8211</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53" s="3">
+        <v>1</v>
+      </c>
+      <c r="J53" s="3">
+        <v>1</v>
+      </c>
+      <c r="K53" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11">
+      <c r="B54" s="23" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="65" spans="2:2">
-      <c r="B65" t="s">
+      <c r="C54" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F54" s="3">
+        <v>8212</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54" s="3">
+        <v>1</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1</v>
+      </c>
+      <c r="K54" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11">
+      <c r="B55" s="23" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="66" spans="2:2">
-      <c r="B66" t="s">
+      <c r="C55" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F55" s="3">
+        <v>8213</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" s="3">
+        <v>1</v>
+      </c>
+      <c r="J55" s="3">
+        <v>1</v>
+      </c>
+      <c r="K55" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11">
+      <c r="B56" s="23" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="2:2">
-      <c r="B67" t="s">
+      <c r="C56" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="3">
+        <v>8214</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H56" s="3">
+        <v>1</v>
+      </c>
+      <c r="J56" s="3">
+        <v>1</v>
+      </c>
+      <c r="K56" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11">
+      <c r="B57" s="23" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="68" spans="2:2">
-      <c r="B68" t="s">
+      <c r="C57" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="3">
+        <v>8215</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1</v>
+      </c>
+      <c r="K57" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11">
+      <c r="B58" s="23" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="69" spans="2:2">
-      <c r="B69" t="s">
+      <c r="C58" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="3">
+        <v>8216</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1</v>
+      </c>
+      <c r="K58" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11">
+      <c r="B59" s="23" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="70" spans="2:2">
-      <c r="B70" t="s">
+      <c r="C59" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="71" spans="2:2">
-      <c r="B71" t="s">
+      <c r="F59" s="3">
+        <v>8217</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K59" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11">
+      <c r="B60" s="23" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="72" spans="2:2">
-      <c r="B72" t="s">
+      <c r="C60" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60" s="3">
+        <v>8218</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" s="3">
+        <v>1</v>
+      </c>
+      <c r="J60" s="3">
+        <v>1</v>
+      </c>
+      <c r="K60" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11">
+      <c r="B61" s="23" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="73" spans="2:2">
-      <c r="B73" t="s">
+      <c r="C61" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="3">
+        <v>8219</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H61" s="3">
+        <v>1</v>
+      </c>
+      <c r="J61" s="3">
+        <v>1</v>
+      </c>
+      <c r="K61" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11">
+      <c r="B62" s="23" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="74" spans="2:2">
-      <c r="B74" s="23"/>
-    </row>
-    <row r="75" spans="2:2">
-      <c r="B75" s="23"/>
-    </row>
-    <row r="76" spans="2:2">
-      <c r="B76" s="23"/>
-    </row>
-    <row r="77" spans="2:2">
-      <c r="B77" s="23"/>
-    </row>
-    <row r="78" spans="2:2">
-      <c r="B78" s="23"/>
-    </row>
-    <row r="79" spans="2:2">
-      <c r="B79" s="23"/>
-    </row>
-    <row r="80" spans="2:2">
-      <c r="B80" s="23"/>
+      <c r="C62" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="3">
+        <v>8220</v>
+      </c>
+      <c r="G62" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1</v>
+      </c>
+      <c r="K62" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11">
+      <c r="B63" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C63" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F63" s="3">
+        <v>8221</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63" s="3">
+        <v>1</v>
+      </c>
+      <c r="J63" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K63" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11">
+      <c r="B64" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="C64" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F64" s="3">
+        <v>8222</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" s="3">
+        <v>1</v>
+      </c>
+      <c r="J64" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="K64" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11">
+      <c r="B65" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C65" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F65" s="3">
+        <v>8223</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H65" s="3">
+        <v>2</v>
+      </c>
+      <c r="J65" s="3">
+        <v>2</v>
+      </c>
+      <c r="K65" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11">
+      <c r="B66" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C66" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F66" s="3">
+        <v>8225</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66" s="3">
+        <v>2</v>
+      </c>
+      <c r="J66" s="3">
+        <v>2</v>
+      </c>
+      <c r="K66" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11">
+      <c r="B67" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C67" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67" s="3">
+        <v>8227</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67" s="3">
+        <v>1</v>
+      </c>
+      <c r="J67" s="3">
+        <v>1</v>
+      </c>
+      <c r="K67" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11">
+      <c r="B68" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" s="3">
+        <v>8228</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H68" s="3">
+        <v>1</v>
+      </c>
+      <c r="J68" s="3">
+        <v>1</v>
+      </c>
+      <c r="K68" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11">
+      <c r="B69" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C69" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69" s="3">
+        <v>8229</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69" s="3">
+        <v>1</v>
+      </c>
+      <c r="J69" s="3">
+        <v>1</v>
+      </c>
+      <c r="K69" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11">
+      <c r="B70" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C70" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F70" s="3">
+        <v>8230</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H70" s="3">
+        <v>1</v>
+      </c>
+      <c r="J70" s="3">
+        <v>1</v>
+      </c>
+      <c r="K70" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11">
+      <c r="B71" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="C71" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F71" s="3">
+        <v>8231</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H71" s="3">
+        <v>1</v>
+      </c>
+      <c r="J71" s="3">
+        <v>1</v>
+      </c>
+      <c r="K71" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" s="15" customFormat="1" spans="2:11">
+      <c r="B72" s="28"/>
+    </row>
+    <row r="73" spans="2:11">
+      <c r="B73" s="29"/>
+    </row>
+    <row r="74" spans="2:11">
+      <c r="B74" s="29"/>
+    </row>
+    <row r="75" spans="2:11">
+      <c r="B75" s="29"/>
+    </row>
+    <row r="76" spans="2:11">
+      <c r="B76" s="29"/>
+    </row>
+    <row r="77" spans="2:11">
+      <c r="B77" s="29"/>
+    </row>
+    <row r="78" spans="2:11">
+      <c r="B78" s="29"/>
+    </row>
+    <row r="79" spans="2:11">
+      <c r="B79" s="29"/>
+    </row>
+    <row r="80" spans="2:11">
+      <c r="B80" s="29"/>
     </row>
     <row r="81" spans="2:2">
-      <c r="B81" s="23"/>
+      <c r="B81" s="29"/>
     </row>
     <row r="82" spans="2:2">
-      <c r="B82" s="23"/>
-    </row>
-    <row r="83" spans="2:2">
-      <c r="B83" s="23"/>
+      <c r="B82" s="29"/>
     </row>
     <row r="84" spans="2:2">
-      <c r="B84" s="23"/>
+      <c r="B84" s="29"/>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="29"/>
     </row>
     <row r="86" spans="2:2">
-      <c r="B86" s="23"/>
+      <c r="B86" s="29"/>
     </row>
     <row r="87" spans="2:2">
-      <c r="B87" s="23"/>
+      <c r="B87" s="29"/>
     </row>
     <row r="88" spans="2:2">
-      <c r="B88" s="23"/>
+      <c r="B88" s="29"/>
     </row>
     <row r="89" spans="2:2">
-      <c r="B89" s="23"/>
+      <c r="B89" s="29"/>
     </row>
     <row r="90" spans="2:2">
-      <c r="B90" s="23"/>
+      <c r="B90" s="29"/>
     </row>
     <row r="91" spans="2:2">
-      <c r="B91" s="23"/>
+      <c r="B91" s="29"/>
     </row>
     <row r="92" spans="2:2">
-      <c r="B92" s="23"/>
+      <c r="B92" s="29"/>
     </row>
     <row r="93" spans="2:2">
-      <c r="B93" s="23"/>
+      <c r="B93" s="29"/>
     </row>
     <row r="94" spans="2:2">
-      <c r="B94" s="23"/>
+      <c r="B94" s="29"/>
     </row>
     <row r="95" spans="2:2">
-      <c r="B95" s="23"/>
+      <c r="B95" s="29"/>
     </row>
     <row r="96" spans="2:2">
-      <c r="B96" s="23"/>
+      <c r="B96" s="29"/>
     </row>
     <row r="97" spans="2:2">
-      <c r="B97" s="23"/>
+      <c r="B97" s="29"/>
     </row>
     <row r="98" spans="2:2">
-      <c r="B98" s="23"/>
-    </row>
-    <row r="99" spans="2:2">
-      <c r="B99" s="23"/>
+      <c r="B98" s="29"/>
     </row>
     <row r="100" spans="2:2">
-      <c r="B100" s="23"/>
+      <c r="B100" s="29"/>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" s="29"/>
     </row>
     <row r="102" spans="2:2">
-      <c r="B102" s="23"/>
+      <c r="B102" s="29"/>
     </row>
     <row r="103" spans="2:2">
-      <c r="B103" s="23"/>
+      <c r="B103" s="29"/>
     </row>
     <row r="104" spans="2:2">
-      <c r="B104" s="23"/>
+      <c r="B104" s="29"/>
     </row>
     <row r="105" spans="2:2">
-      <c r="B105" s="23"/>
+      <c r="B105" s="29"/>
     </row>
     <row r="106" spans="2:2">
-      <c r="B106" s="23"/>
+      <c r="B106" s="29"/>
     </row>
     <row r="107" spans="2:2">
-      <c r="B107" s="23"/>
+      <c r="B107" s="29"/>
     </row>
     <row r="108" spans="2:2">
-      <c r="B108" s="23"/>
+      <c r="B108" s="29"/>
     </row>
     <row r="109" spans="2:2">
-      <c r="B109" s="23"/>
+      <c r="B109" s="29"/>
     </row>
     <row r="110" spans="2:2">
-      <c r="B110" s="23"/>
+      <c r="B110" s="29"/>
     </row>
     <row r="111" spans="2:2">
-      <c r="B111" s="23"/>
+      <c r="B111" s="29"/>
     </row>
     <row r="112" spans="2:2">
-      <c r="B112" s="23"/>
+      <c r="B112" s="29"/>
     </row>
     <row r="113" spans="2:2">
-      <c r="B113" s="23"/>
+      <c r="B113" s="29"/>
     </row>
     <row r="114" spans="2:2">
-      <c r="B114" s="23"/>
-    </row>
-    <row r="115" spans="2:2">
-      <c r="B115" s="23"/>
+      <c r="B114" s="29"/>
     </row>
     <row r="116" spans="2:2">
-      <c r="B116" s="23"/>
+      <c r="B116" s="30"/>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117" s="30"/>
     </row>
     <row r="118" spans="2:2">
-      <c r="B118" s="24"/>
+      <c r="B118" s="30"/>
     </row>
     <row r="119" spans="2:2">
-      <c r="B119" s="24"/>
+      <c r="B119" s="30"/>
     </row>
     <row r="120" spans="2:2">
-      <c r="B120" s="24"/>
+      <c r="B120" s="30"/>
     </row>
     <row r="121" spans="2:2">
-      <c r="B121" s="24"/>
+      <c r="B121" s="30"/>
     </row>
     <row r="122" spans="2:2">
-      <c r="B122" s="24"/>
+      <c r="B122" s="30"/>
     </row>
     <row r="123" spans="2:2">
-      <c r="B123" s="24"/>
+      <c r="B123" s="30"/>
     </row>
     <row r="124" spans="2:2">
-      <c r="B124" s="24"/>
-    </row>
-    <row r="125" spans="2:2">
-      <c r="B125" s="24"/>
-    </row>
-    <row r="126" spans="2:2">
-      <c r="B126" s="24"/>
+      <c r="B124" s="30"/>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129" s="30"/>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130" s="30"/>
     </row>
     <row r="131" spans="2:2">
-      <c r="B131" s="24"/>
-    </row>
-    <row r="132" spans="2:2">
-      <c r="B132" s="24"/>
-    </row>
-    <row r="133" spans="2:2">
-      <c r="B133" s="24"/>
+      <c r="B131" s="30"/>
+    </row>
+    <row r="224" spans="2:2">
+      <c r="B224" s="29"/>
+    </row>
+    <row r="225" spans="2:2">
+      <c r="B225" s="29"/>
     </row>
     <row r="226" spans="2:2">
-      <c r="B226" s="23"/>
+      <c r="B226" s="29"/>
     </row>
     <row r="227" spans="2:2">
-      <c r="B227" s="23"/>
+      <c r="B227" s="29"/>
     </row>
     <row r="228" spans="2:2">
-      <c r="B228" s="23"/>
+      <c r="B228" s="29"/>
     </row>
     <row r="229" spans="2:2">
-      <c r="B229" s="23"/>
+      <c r="B229" s="29"/>
     </row>
     <row r="230" spans="2:2">
-      <c r="B230" s="23"/>
+      <c r="B230" s="29"/>
     </row>
     <row r="231" spans="2:2">
-      <c r="B231" s="23"/>
+      <c r="B231" s="29"/>
     </row>
     <row r="232" spans="2:2">
-      <c r="B232" s="23"/>
+      <c r="B232" s="29"/>
     </row>
     <row r="233" spans="2:2">
-      <c r="B233" s="23"/>
+      <c r="B233" s="29"/>
     </row>
     <row r="234" spans="2:2">
-      <c r="B234" s="23"/>
+      <c r="B234" s="29"/>
     </row>
     <row r="235" spans="2:2">
-      <c r="B235" s="23"/>
+      <c r="B235" s="29"/>
     </row>
     <row r="236" spans="2:2">
-      <c r="B236" s="23"/>
+      <c r="B236" s="29"/>
     </row>
     <row r="237" spans="2:2">
-      <c r="B237" s="23"/>
+      <c r="B237" s="29"/>
     </row>
     <row r="238" spans="2:2">
-      <c r="B238" s="23"/>
-    </row>
-    <row r="239" spans="2:2">
-      <c r="B239" s="23"/>
-    </row>
-    <row r="240" spans="2:2">
-      <c r="B240" s="23"/>
+      <c r="B238" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3418,22 +4477,22 @@
         <v>1000</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
       <c r="G2" s="10" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="H2" s="10">
         <v>1</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="J2" s="10">
         <v>1</v>
@@ -3565,26 +4624,26 @@
         <v>50000</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="4">
         <v>500</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="H2" s="4">
         <v>1</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="J2" s="4">
         <v>1</v>
@@ -3593,13 +4652,13 @@
         <v>0</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
